--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>09-Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS Côte d'Ivoire</t>
+          <t>INS Côte d'Ivoire (IHPC)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>General government debt, projection</t>
+          <t>Government debt, projection (peak 56.3% in 2025); WAEMU limit 70%</t>
         </is>
       </c>
     </row>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed; no successor arrangement identified</t>
+          <t>EFF/ECF and RSF, completed (sixth and final EFF/ECF review and fifth RSF review, Jun-26); no successor arrangement identified</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS Côte d'Ivoire (IHPC)</t>
+          <t>INS Côte d'Ivoire, IHPC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Government debt, projection (peak 56.3% in 2025); WAEMU limit 70%</t>
+          <t>Government debt, projection; WAEMU ceiling 70%</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026 (budgeted)</t>
+          <t>2026 (budget)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1251,11 +1251,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF and RSF, completed (sixth and final EFF/ECF review and fifth RSF review, Jun-26); no successor arrangement identified</t>
+          <t>EFF/ECF (final sixth reviews completed) and RSF (fifth review completed), Jun-26</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF, Jun-26</t>
+          <t>IMF, 30-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, Jun-26 (2026 budgeted)</t>
+          <t>IMF / Ministry of Finance, 30-Jun-26 (2026 budget)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, Jun-26</t>
+          <t>IMF / Ministry of Finance, 30-Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS Côte d'Ivoire, IHPC</t>
+          <t>INS Côte d'Ivoire (IHPC)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF, Jun-26</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance</t>
+          <t>IMF / Ministry of Finance, Jun-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026 (budget)</t>
+          <t>2026 (budgeted)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance</t>
+          <t>IMF / Ministry of Finance, Jun-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (final sixth reviews completed) and RSF (fifth review completed), Jun-26</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B); final reviews completed</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1339,7 +1339,7 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF, 30-Jun-26</t>
+          <t>IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 30-Jun-26 (2026 budget)</t>
+          <t>IMF / Ministry of Finance, Jun-26 (2026 budgeted)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF / Ministry of Finance, 30-Jun-26</t>
+          <t>IMF / Ministry of Finance, Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BCEAO Monetary Policy Committee</t>
+          <t>BCEAO Monetary Policy Committee communiqué</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INS Côte d'Ivoire (IHPC)</t>
+          <t>INS Côte d'Ivoire, IHPC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Government debt, projection; WAEMU ceiling 70%</t>
+          <t>General government debt, projection</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF WEO (data record)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>World Bank WDI (data record)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF WEO (data record)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B); final reviews completed</t>
+          <t>EFF/ECF (US$3.5B) and RSF (US$1.3B), final reviews completed; no successor arrangement identified</t>
         </is>
       </c>
       <c r="C33" t="n">

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
+++ b/models/sovereigns/C_te_d_Ivoire_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/cote-d-ivoire.json</t>
         </is>
       </c>
     </row>
